--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62198625</v>
+        <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljusmon, Ång</t>
+          <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637865</v>
+        <v>637895</v>
       </c>
       <c r="R2" t="n">
-        <v>7012498</v>
+        <v>7012507</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-01</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-01</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,24 +775,3210 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Askia Sandberg</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Askia Sandberg</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137124330</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137124334</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93422</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>638103</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7012331</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124334</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137132726</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93422</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>638003</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7012353</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132726</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137124325</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>637874</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7012654</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124325</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137124329</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>637895</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7012523</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124329</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137124332</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>638009</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7012351</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124332</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137132722</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>637868</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7012591</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132722</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137132727</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>638091</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7012318</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132727</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137132729</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>638116</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7012337</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132729</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137132730</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>638118</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7012322</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132730</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137132731</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>638119</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7012331</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132731</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137132733</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>637938</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7012370</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132733</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137132720</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79507</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>637898</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7012644</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132720</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137132721</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79507</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>637871</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7012641</v>
+      </c>
+      <c r="S15" t="n">
+        <v>14</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132721</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>62198625</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ljusmon, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>637865</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7012498</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2016-06-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2016-06-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Askia Sandberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Askia Sandberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/62198625</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137124327</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80102</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>637893</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7012592</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124327</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137124331</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80102</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>637908</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7012497</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124331</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137124326</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79241</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>637879</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7012641</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124326</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137124328</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79241</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>637889</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7012589</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124328</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137132718</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>637920</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7012648</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132718</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137132719</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>637911</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7012646</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132719</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137132723</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>637888</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7012585</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132723</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137132724</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>637901</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7012524</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132724</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137132725</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>637972</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7012434</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132725</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137132728</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>638088</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7012307</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132728</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137132732</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>638111</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7012320</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132732</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -3038,11 +3038,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3173,11 +3169,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3308,11 +3300,7 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3443,11 +3431,7 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3578,11 +3562,7 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3713,11 +3693,7 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3848,11 +3824,7 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18697-2025 artfynd.xlsx
+++ b/artfynd/A 18697-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124330</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124334</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132726</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137124325</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137124329</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>137124332</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137132722</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>137132727</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>137132729</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>137132730</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137132731</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>137132733</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137132720</v>
       </c>
       <c r="B14" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137132721</v>
       </c>
       <c r="B15" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>137124327</v>
       </c>
       <c r="B17" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>137124331</v>
       </c>
       <c r="B18" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>137124326</v>
       </c>
       <c r="B19" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137124328</v>
       </c>
       <c r="B20" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>137132718</v>
       </c>
       <c r="B21" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>137132719</v>
       </c>
       <c r="B22" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>137132723</v>
       </c>
       <c r="B23" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>137132724</v>
       </c>
       <c r="B24" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>137132725</v>
       </c>
       <c r="B25" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>137132728</v>
       </c>
       <c r="B26" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>137132732</v>
       </c>
       <c r="B27" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
